--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="304">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>IHE-PCC - Coded Social History Section. Liste codée des informations relatives aux habitus et au mode de vie du patient.</t>
+    <t>IHE-PCC - Coded Social History Section. Liste codÃ©e des informations relatives aux habitus et au mode de vie du patient.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -411,7 +411,7 @@
     <t>ccdSectionCodedSocialHistory</t>
   </si>
   <si>
-    <t>Conformité Social History Section (CCD)</t>
+    <t>ConformitÃ© Social History Section (CCD)</t>
   </si>
   <si>
     <t>Section.templateId:ccdSectionCodedSocialHistory.nullFlavor</t>
@@ -456,7 +456,7 @@
     <t>iheSectionCodedSocialHistory</t>
   </si>
   <si>
-    <t>Conformité Social History Section (IHE-PCC)</t>
+    <t>ConformitÃ© Social History Section (IHE-PCC)</t>
   </si>
   <si>
     <t>Section.templateId:iheSectionCodedSocialHistory.nullFlavor</t>
@@ -483,7 +483,7 @@
     <t>frSectionHabitusModeDeVie</t>
   </si>
   <si>
-    <t>Conformité FR-Habitus-Mode-de-Vie (CI-SIS)</t>
+    <t>ConformitÃ© FR-Habitus-Mode-de-Vie (CI-SIS)</t>
   </si>
   <si>
     <t>Section.templateId:frSectionHabitusModeDeVie.nullFlavor</t>
@@ -556,10 +556,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -768,7 +771,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée Habitus, Mode de vie</t>
+    <t>EntrÃ©e Habitus, Mode de vie</t>
   </si>
   <si>
     <t>Section.entry.nullFlavor</t>
@@ -5210,7 +5213,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>175</v>
       </c>
@@ -5229,7 +5232,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5240,8 +5243,12 @@
       <c r="K39" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
+      <c r="L39" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5311,10 +5318,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5328,7 +5335,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5337,13 +5344,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5394,7 +5401,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5414,10 +5421,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5513,12 +5520,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5528,13 +5535,13 @@
         <v>62</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5547,7 +5554,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5559,7 +5566,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5598,7 +5605,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5616,28 +5623,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5650,7 +5657,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5662,7 +5669,7 @@
         <v>74</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>74</v>
@@ -5701,7 +5708,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5721,17 +5728,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5753,7 +5760,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5765,7 +5772,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -5804,7 +5811,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5824,17 +5831,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5856,7 +5863,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5907,7 +5914,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5925,28 +5932,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5959,7 +5966,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5971,7 +5978,7 @@
         <v>74</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>74</v>
@@ -6010,7 +6017,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6030,10 +6037,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6056,11 +6063,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6111,7 +6118,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6131,10 +6138,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6161,7 +6168,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6212,7 +6219,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6232,17 +6239,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6260,11 +6267,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6315,7 +6322,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6335,17 +6342,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6363,11 +6370,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6418,7 +6425,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6438,17 +6445,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6466,11 +6473,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6521,7 +6528,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6541,10 +6548,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6558,7 +6565,7 @@
         <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6567,13 +6574,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6624,7 +6631,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6644,10 +6651,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6661,7 +6668,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6670,13 +6677,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6727,7 +6734,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6747,10 +6754,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6773,7 +6780,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6826,7 +6833,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6846,10 +6853,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6905,25 +6912,25 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6943,10 +6950,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6969,7 +6976,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7022,7 +7029,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7042,10 +7049,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7068,7 +7075,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7121,7 +7128,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7141,10 +7148,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7167,7 +7174,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7220,7 +7227,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7240,10 +7247,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7257,7 +7264,7 @@
         <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7266,10 +7273,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7321,7 +7328,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7341,10 +7348,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7442,10 +7449,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7543,10 +7550,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7644,10 +7651,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7745,10 +7752,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7848,10 +7855,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7951,10 +7958,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8054,10 +8061,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8157,10 +8164,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8258,10 +8265,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8291,7 +8298,7 @@
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
@@ -8317,7 +8324,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8335,7 +8342,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8355,10 +8362,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8392,7 +8399,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>74</v>
@@ -8434,7 +8441,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8454,10 +8461,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8480,7 +8487,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8533,7 +8540,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8553,10 +8560,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8579,7 +8586,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8632,7 +8639,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8652,10 +8659,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8678,7 +8685,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8731,7 +8738,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8751,10 +8758,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8777,7 +8784,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8830,7 +8837,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8850,10 +8857,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8876,7 +8883,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8929,7 +8936,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8949,10 +8956,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8975,7 +8982,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9028,7 +9035,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9048,10 +9055,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9074,7 +9081,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9127,7 +9134,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9147,10 +9154,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9173,7 +9180,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9226,7 +9233,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9246,10 +9253,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9272,7 +9279,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9325,7 +9332,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9345,10 +9352,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9371,7 +9378,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9424,7 +9431,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9444,10 +9451,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9545,10 +9552,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9646,10 +9653,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9747,10 +9754,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9848,10 +9855,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9951,10 +9958,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10054,10 +10061,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10157,10 +10164,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10260,10 +10267,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10361,10 +10368,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10391,7 +10398,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10400,7 +10407,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>74</v>
@@ -10442,7 +10449,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10462,10 +10469,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10499,7 +10506,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>74</v>
@@ -10541,7 +10548,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10561,10 +10568,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10587,7 +10594,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10640,7 +10647,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
